--- a/legal_forms/006_legal_services_payment_form--legal_forms.xlsx
+++ b/legal_forms/006_legal_services_payment_form--legal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'court_fee'}</t>
+          <t>court_fee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Court Fee'}</t>
+          <t>Court Fee</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'consultation'}</t>
+          <t>consultation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Consultation'}</t>
+          <t>Consultation</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'document_review'}</t>
+          <t>document_review</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Document Review'}</t>
+          <t>Document Review</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'document_preparation'}</t>
+          <t>document_preparation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Document Preparation'}</t>
+          <t>Document Preparation</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'document_review_plus'}</t>
+          <t>document_review_plus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Document Review Plus'}</t>
+          <t>Document Review Plus</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'document_preparation_plus'}</t>
+          <t>document_preparation_plus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Document Preparation Plus'}</t>
+          <t>Document Preparation Plus</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'online_payment'}</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Online Payment'}</t>
+          <t>Online Payment</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'unpaid'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Unpaid'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
